--- a/data/reports/W10_2026.xlsx
+++ b/data/reports/W10_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\RMIT_WORKS\TEAM\WIP\GIT\RMIT_WIP\data\reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{993DBF94-B6A3-41EC-977C-2748DD3C74C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EACC6877-DD99-4CF0-8411-4E67F67AFC0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="733" yWindow="-118" windowWidth="32898" windowHeight="21181" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -132,9 +132,6 @@
     <t>Trinh/Danh</t>
   </si>
   <si>
-    <t>2026 Open Day Style Guide</t>
-  </si>
-  <si>
     <t>Trinh/Danh/Tran</t>
   </si>
   <si>
@@ -229,6 +226,9 @@
   </si>
   <si>
     <t>20" Animation videos</t>
+  </si>
+  <si>
+    <t>2026 INTON Open Day Style Guide</t>
   </si>
 </sst>
 </file>
@@ -768,7 +768,7 @@
         <v>5</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F3" s="12"/>
     </row>
@@ -786,7 +786,7 @@
         <v>5</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F4" s="12"/>
     </row>
@@ -795,7 +795,7 @@
         <v>27</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>9</v>
@@ -804,7 +804,7 @@
         <v>5</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F5" s="12"/>
     </row>
@@ -813,7 +813,7 @@
         <v>27</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C6" s="5" t="s">
         <v>7</v>
@@ -831,16 +831,16 @@
         <v>27</v>
       </c>
       <c r="B7" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="E7" s="5" t="s">
         <v>58</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>59</v>
       </c>
       <c r="F7" s="12"/>
     </row>
@@ -849,16 +849,16 @@
         <v>27</v>
       </c>
       <c r="B8" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="C8" s="5" t="s">
         <v>32</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>33</v>
       </c>
       <c r="D8" s="5" t="s">
         <v>6</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F8" s="12"/>
     </row>
@@ -867,7 +867,7 @@
         <v>13</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>8</v>
@@ -876,34 +876,34 @@
         <v>12</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F9" s="12"/>
     </row>
     <row r="10" spans="1:6" s="5" customFormat="1" ht="18.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="C10" s="5" t="s">
         <v>38</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>39</v>
       </c>
       <c r="D10" s="5" t="s">
         <v>11</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F10" s="12"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>8</v>
@@ -912,15 +912,15 @@
         <v>5</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B12" s="5" t="s">
         <v>43</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>44</v>
       </c>
       <c r="C12" s="5" t="s">
         <v>10</v>
@@ -934,10 +934,10 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>29</v>
@@ -951,10 +951,10 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B14" s="5" t="s">
         <v>46</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>47</v>
       </c>
       <c r="C14" s="5" t="s">
         <v>8</v>
@@ -968,10 +968,10 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C15" s="5" t="s">
         <v>8</v>
@@ -980,15 +980,15 @@
         <v>5</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C16" s="5" t="s">
         <v>29</v>
@@ -997,7 +997,7 @@
         <v>5</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
@@ -1021,7 +1021,7 @@
         <v>5</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F18" s="12"/>
     </row>
@@ -1030,7 +1030,7 @@
         <v>13</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>10</v>
@@ -1039,7 +1039,7 @@
         <v>12</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F19" s="12"/>
     </row>
@@ -1057,7 +1057,7 @@
         <v>5</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F20" s="12"/>
     </row>
@@ -1066,7 +1066,7 @@
         <v>19</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C21" s="5" t="s">
         <v>10</v>
@@ -1075,7 +1075,7 @@
         <v>12</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F21" s="12"/>
     </row>
@@ -1097,7 +1097,7 @@
         <v>6</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F23" s="12"/>
     </row>
@@ -1119,7 +1119,7 @@
         <v>5</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F25" s="12"/>
     </row>
@@ -1137,7 +1137,7 @@
         <v>6</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">

--- a/data/reports/W10_2026.xlsx
+++ b/data/reports/W10_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\RMIT_WORKS\TEAM\WIP\GIT\RMIT_WIP\data\reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EACC6877-DD99-4CF0-8411-4E67F67AFC0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{966A3801-0EA7-44F8-B4C7-68F7F12C2106}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="733" yWindow="-118" windowWidth="32898" windowHeight="21181" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="66">
   <si>
     <t>Campaign (group)</t>
   </si>
@@ -229,6 +229,9 @@
   </si>
   <si>
     <t>2026 INTON Open Day Style Guide</t>
+  </si>
+  <si>
+    <t>Highlight</t>
   </si>
 </sst>
 </file>
@@ -880,7 +883,7 @@
       </c>
       <c r="F9" s="12"/>
     </row>
-    <row r="10" spans="1:6" s="5" customFormat="1" ht="18.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" s="5" customFormat="1" ht="17.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
         <v>37</v>
       </c>
@@ -896,7 +899,9 @@
       <c r="E10" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="F10" s="12"/>
+      <c r="F10" s="12" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
